--- a/Result/checksun_type/支付.xlsx
+++ b/Result/checksun_type/支付.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>538.2</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>552.05</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>576.4</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>552.05</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>576.4</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>32864382.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>40930647.2</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>40930647.2</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>44524261.4</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>46680868.86</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>46680868.86</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>-1953670.607991926</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>32864382</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>32864382.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>533.2</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>552.3</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>577.48</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>552.3</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>577.48</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>46463751.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>36189476.0</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>36189476</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>45465653.4</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>47624299.32</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>47624299.32</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>-1355210.902363062</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>46463751</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>46463751.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>530.4</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>553.5</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>578.86</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>553.5</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>578.86</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>12613596.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>43859460.8</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>43859460.8</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>49334872.8</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>50438799.18</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>50438799.18</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>-1908943.32638029</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>12613596</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>12613596.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>533.2</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>555.95</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>580.36</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>555.95</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>580.36</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>58932053.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>47741874.4</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>47741874.4</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>50227359.5</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>51664282.3</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>51664282.3</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>994989.2223943844</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>58932053</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>58932053.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>537.8</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>558.85</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>581.72</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>558.85</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>581.72</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>53779454.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>44871115.8</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>44871115.8</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>47583455.9</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>51600106.7</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>51600106.7</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>145237.1412727013</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>53779454</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>53779454.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>539.2</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>561.05</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>582.82</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>561.05</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>582.8200000000001</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>9158526.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>48117875.6</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>48117875.6</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>51575864.2</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>52456694.28</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>52456694.28</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>-521817.2653751597</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>9158526</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>9158526.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>544.8</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>563.8</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>584.12</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>563.8</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>584.12</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>84813675.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>54741830.8</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>54741830.8</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>55961046.9</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>53665729.24</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>53665729.24</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>3324697.913177006</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>84813675</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>84813675.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>552.4</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>565.8</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>585.52</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>565.8</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>585.52</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>32025664.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>54810284.8</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>54810284.8</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>50917066.6</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>53133474.32</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>53133474.32</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>595071.5642095059</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>32025664</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>32025664.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>556.4</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>567.35</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>586.7</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>567.35</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>586.7</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>44578260.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>52712844.6</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>52712844.6</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>49263413.2</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>54961949.54</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>54961949.54</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>2330211.116962738</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>44578260</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>44578260.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>560.0</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>568.6</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>587.78</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>568.6</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>587.78</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>70013253.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>50295796.0</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>50295796</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>49903580.7</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>56198727.74</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>56198727.74</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>3380839.081004396</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>70013253</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>70013253.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>564.0</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>569.75</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>589.04</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>569.75</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>589.04</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>42278302.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>55033852.8</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>55033852.8</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>47287033.4</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>56418593.66</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>56418593.66</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>2035814.098170899</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>42278302</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>42278302.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>57.14</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>60.68</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>60.07</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>60.68</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>60.07</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>53945.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>41076.8</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>41076.8</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>75787.6</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>133384.92</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>133384.92</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>-43185.05540683233</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>53945</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>53945.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>57.04</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>60.78</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>60.08</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>60.78</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>60.08</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>31367.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>40032.4</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>40032.4</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>84967.9</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>133252.88</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>133252.88</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>-45774.36002204588</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>31367</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>31367.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>57.16</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>60.95</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>60.15</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>60.95</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>60.15</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>39674.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>54189.8</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>54189.8</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>92630.7</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>133923.72</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>133923.72</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>-45419.49661442071</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>39674</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>39674.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>57.8</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>61.18</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>60.21</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>61.18</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>60.21</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>46910.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>62009.0</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>62009</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>108151.7</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>133938.68</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>133938.68</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>-44180.45972444121</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>46910</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>46910.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>58.76000000000001</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>61.49</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>60.27</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>61.49</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>60.27</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>33488.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>87127.8</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>87127.8</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>132071.0</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>133588.72</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>133588.72</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>-41607.81917716903</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>33488</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>33488.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>59.92</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>61.76</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>60.3</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>61.76</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>60.3</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>48723.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>110498.4</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>110498.4</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>215595.9</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>133380.62</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>133380.62</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>-35008.55342473843</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>48723</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>48723.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>60.92</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>61.99</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>60.32</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>61.99</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>60.32</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>102154.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>129903.4</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>129903.4</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>432254.2</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>132909.26</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>132909.26</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>-25963.04687038265</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>102154</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>102154.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>61.5</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>62.2</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>60.34</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>62.2</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>60.34</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>78770.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>131071.6</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>131071.6</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>460267.8</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>131193.3</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>131193.3</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>-17838.39297593216</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>78770</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>78770.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>61.9</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>62.36</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>60.32</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>62.36</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>60.32</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>172504.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>154294.4</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>154294.4</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>454494.8</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>130731.54</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>130731.54</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>-3089.230520433863</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>172504</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>172504.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9657,11 @@
           <t>62.72000000000001</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>62.37</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>60.29</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>62.37</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>60.29</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9708,16 @@
           <t>150341.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>177014.2</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>177014.2</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>439664.0</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>128549.96</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>128549.96</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>8048.402648864896</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>150341</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>150341.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>63.56</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>62.24</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>60.23</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>62.24</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>60.23</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>145748.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>320693.4</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>320693.4</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>429650.2</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>126749.76</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>126749.76</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>26046.47136754659</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>145748</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>145748.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10465,7 +10333,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -10649,15 +10517,11 @@
           <t>74.24</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>75.94</t>
-        </is>
-      </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>78.82</t>
-        </is>
+      <c r="AM24" t="n">
+        <v>75.94</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>78.81999999999999</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
@@ -10704,20 +10568,16 @@
           <t>709.0</t>
         </is>
       </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>378.4</t>
-        </is>
+      <c r="AX24" t="n">
+        <v>378.4</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
           <t>754.4</t>
         </is>
       </c>
-      <c r="AZ24" t="inlineStr">
-        <is>
-          <t>1063.24</t>
-        </is>
+      <c r="AZ24" t="n">
+        <v>1063.24</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
@@ -10734,8 +10594,10 @@
           <t>-65.36342660409002</t>
         </is>
       </c>
-      <c r="BD24" t="n">
-        <v>709</v>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>709.0</t>
+        </is>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
@@ -10901,7 +10763,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11085,15 +10947,11 @@
           <t>74.06</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>76.03</t>
-        </is>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>78.98</t>
-        </is>
+      <c r="AM25" t="n">
+        <v>76.03</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>78.98</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
@@ -11140,20 +10998,16 @@
           <t>384.0</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>555.6</t>
-        </is>
+      <c r="AX25" t="n">
+        <v>555.6</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
           <t>684.0</t>
         </is>
       </c>
-      <c r="AZ25" t="inlineStr">
-        <is>
-          <t>1078.44</t>
-        </is>
+      <c r="AZ25" t="n">
+        <v>1078.44</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
@@ -11170,8 +11024,10 @@
           <t>-81.31309747373018</t>
         </is>
       </c>
-      <c r="BD25" t="n">
-        <v>384</v>
+      <c r="BD25" t="inlineStr">
+        <is>
+          <t>384.0</t>
+        </is>
       </c>
       <c r="BE25" t="inlineStr">
         <is>
@@ -11337,7 +11193,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11521,15 +11377,11 @@
           <t>74.1</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>76.2</t>
-        </is>
-      </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>79.17</t>
-        </is>
+      <c r="AM26" t="n">
+        <v>76.2</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>79.17</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
@@ -11576,20 +11428,16 @@
           <t>189.0</t>
         </is>
       </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>1003.4</t>
-        </is>
+      <c r="AX26" t="n">
+        <v>1003.4</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
           <t>665.3</t>
         </is>
       </c>
-      <c r="AZ26" t="inlineStr">
-        <is>
-          <t>1085.84</t>
-        </is>
+      <c r="AZ26" t="n">
+        <v>1085.84</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
@@ -11606,8 +11454,10 @@
           <t>-66.3728738062972</t>
         </is>
       </c>
-      <c r="BD26" t="n">
-        <v>189</v>
+      <c r="BD26" t="inlineStr">
+        <is>
+          <t>189.0</t>
+        </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
@@ -11773,7 +11623,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11957,15 +11807,11 @@
           <t>74.74</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>76.39</t>
-        </is>
-      </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>79.33</t>
-        </is>
+      <c r="AM27" t="n">
+        <v>76.39</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>79.33</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
@@ -12012,20 +11858,16 @@
           <t>461.0</t>
         </is>
       </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>997.0</t>
-        </is>
+      <c r="AX27" t="n">
+        <v>997</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
           <t>732.8</t>
         </is>
       </c>
-      <c r="AZ27" t="inlineStr">
-        <is>
-          <t>1111.82</t>
-        </is>
+      <c r="AZ27" t="n">
+        <v>1111.82</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
@@ -12042,8 +11884,10 @@
           <t>-21.76638021688211</t>
         </is>
       </c>
-      <c r="BD27" t="n">
-        <v>461</v>
+      <c r="BD27" t="inlineStr">
+        <is>
+          <t>461.0</t>
+        </is>
       </c>
       <c r="BE27" t="inlineStr">
         <is>
@@ -12209,7 +12053,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -12393,15 +12237,11 @@
           <t>75.54</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>76.6</t>
-        </is>
-      </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>79.51</t>
-        </is>
+      <c r="AM28" t="n">
+        <v>76.59999999999999</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>79.51000000000001</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
@@ -12448,20 +12288,16 @@
           <t>149.0</t>
         </is>
       </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>1109.8</t>
-        </is>
+      <c r="AX28" t="n">
+        <v>1109.8</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
           <t>833.5</t>
         </is>
       </c>
-      <c r="AZ28" t="inlineStr">
-        <is>
-          <t>1227.54</t>
-        </is>
+      <c r="AZ28" t="n">
+        <v>1227.54</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
@@ -12478,8 +12314,10 @@
           <t>13.59169563288503</t>
         </is>
       </c>
-      <c r="BD28" t="n">
-        <v>149</v>
+      <c r="BD28" t="inlineStr">
+        <is>
+          <t>149.0</t>
+        </is>
       </c>
       <c r="BE28" t="inlineStr">
         <is>
@@ -12645,7 +12483,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -12829,15 +12667,11 @@
           <t>76.02000000000001</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>76.72</t>
-        </is>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>79.69</t>
-        </is>
+      <c r="AM29" t="n">
+        <v>76.72</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>79.69</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
@@ -12884,20 +12718,16 @@
           <t>1595.0</t>
         </is>
       </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>1130.4</t>
-        </is>
+      <c r="AX29" t="n">
+        <v>1130.4</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
           <t>970.4</t>
         </is>
       </c>
-      <c r="AZ29" t="inlineStr">
-        <is>
-          <t>1231.96</t>
-        </is>
+      <c r="AZ29" t="n">
+        <v>1231.96</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
@@ -12914,8 +12744,10 @@
           <t>97.04638628852092</t>
         </is>
       </c>
-      <c r="BD29" t="n">
-        <v>1595</v>
+      <c r="BD29" t="inlineStr">
+        <is>
+          <t>1595.0</t>
+        </is>
       </c>
       <c r="BE29" t="inlineStr">
         <is>
@@ -13081,7 +12913,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -13265,15 +13097,11 @@
           <t>76.67999999999999</t>
         </is>
       </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>76.82</t>
-        </is>
-      </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>79.87</t>
-        </is>
+      <c r="AM30" t="n">
+        <v>76.81999999999999</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>79.87</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
@@ -13320,20 +13148,16 @@
           <t>2623.0</t>
         </is>
       </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>812.4</t>
-        </is>
+      <c r="AX30" t="n">
+        <v>812.4</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
           <t>872.2</t>
         </is>
       </c>
-      <c r="AZ30" t="inlineStr">
-        <is>
-          <t>1215.96</t>
-        </is>
+      <c r="AZ30" t="n">
+        <v>1215.96</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
@@ -13350,8 +13174,10 @@
           <t>57.87285914341066</t>
         </is>
       </c>
-      <c r="BD30" t="n">
-        <v>2623</v>
+      <c r="BD30" t="inlineStr">
+        <is>
+          <t>2623.0</t>
+        </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
@@ -13517,7 +13343,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -13701,15 +13527,11 @@
           <t>77.26000000000002</t>
         </is>
       </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>76.88</t>
-        </is>
-      </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>80.05</t>
-        </is>
+      <c r="AM31" t="n">
+        <v>76.88</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>80.05</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
@@ -13756,20 +13578,16 @@
           <t>157.0</t>
         </is>
       </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>327.2</t>
-        </is>
+      <c r="AX31" t="n">
+        <v>327.2</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
           <t>724.2</t>
         </is>
       </c>
-      <c r="AZ31" t="inlineStr">
-        <is>
-          <t>1165.2</t>
-        </is>
+      <c r="AZ31" t="n">
+        <v>1165.2</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
@@ -13786,8 +13604,10 @@
           <t>-110.2990674618686</t>
         </is>
       </c>
-      <c r="BD31" t="n">
-        <v>157</v>
+      <c r="BD31" t="inlineStr">
+        <is>
+          <t>157.0</t>
+        </is>
       </c>
       <c r="BE31" t="inlineStr">
         <is>
@@ -13953,7 +13773,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -14137,15 +13957,11 @@
           <t>77.3</t>
         </is>
       </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>76.79</t>
-        </is>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>80.17</t>
-        </is>
+      <c r="AM32" t="n">
+        <v>76.79000000000001</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>80.17</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
@@ -14192,20 +14008,16 @@
           <t>1025.0</t>
         </is>
       </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>468.6</t>
-        </is>
+      <c r="AX32" t="n">
+        <v>468.6</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
           <t>767.1</t>
         </is>
       </c>
-      <c r="AZ32" t="inlineStr">
-        <is>
-          <t>1165.84</t>
-        </is>
+      <c r="AZ32" t="n">
+        <v>1165.84</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
@@ -14222,8 +14034,10 @@
           <t>-82.39113877434352</t>
         </is>
       </c>
-      <c r="BD32" t="n">
-        <v>1025</v>
+      <c r="BD32" t="inlineStr">
+        <is>
+          <t>1025.0</t>
+        </is>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
@@ -14389,7 +14203,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -14573,15 +14387,11 @@
           <t>77.14000000000001</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>76.71</t>
-        </is>
-      </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>80.29</t>
-        </is>
+      <c r="AM33" t="n">
+        <v>76.70999999999999</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>80.29000000000001</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
@@ -14628,20 +14438,16 @@
           <t>252.0</t>
         </is>
       </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>557.2</t>
-        </is>
+      <c r="AX33" t="n">
+        <v>557.2</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
           <t>750.8</t>
         </is>
       </c>
-      <c r="AZ33" t="inlineStr">
-        <is>
-          <t>1161.16</t>
-        </is>
+      <c r="AZ33" t="n">
+        <v>1161.16</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
@@ -14658,8 +14464,10 @@
           <t>-132.5801285502242</t>
         </is>
       </c>
-      <c r="BD33" t="n">
-        <v>252</v>
+      <c r="BD33" t="inlineStr">
+        <is>
+          <t>252.0</t>
+        </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
@@ -14825,7 +14633,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -15009,15 +14817,11 @@
           <t>77.0</t>
         </is>
       </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>76.63</t>
-        </is>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>80.44</t>
-        </is>
+      <c r="AM34" t="n">
+        <v>76.63</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>80.44</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
@@ -15064,20 +14868,16 @@
           <t>5.0</t>
         </is>
       </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>810.4</t>
-        </is>
+      <c r="AX34" t="n">
+        <v>810.4</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
           <t>743.3</t>
         </is>
       </c>
-      <c r="AZ34" t="inlineStr">
-        <is>
-          <t>1172.74</t>
-        </is>
+      <c r="AZ34" t="n">
+        <v>1172.74</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
@@ -15094,8 +14894,10 @@
           <t>-116.7222522104029</t>
         </is>
       </c>
-      <c r="BD34" t="n">
-        <v>5</v>
+      <c r="BD34" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>
@@ -15261,7 +15063,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -15445,15 +15247,11 @@
           <t>96.52000000000001</t>
         </is>
       </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>98.96</t>
-        </is>
-      </c>
-      <c r="AN35" t="inlineStr">
-        <is>
-          <t>102.51</t>
-        </is>
+      <c r="AM35" t="n">
+        <v>98.95999999999999</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>102.51</v>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
@@ -15500,20 +15298,16 @@
           <t>7916.0</t>
         </is>
       </c>
-      <c r="AX35" t="inlineStr">
-        <is>
-          <t>38834.0</t>
-        </is>
+      <c r="AX35" t="n">
+        <v>38834</v>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
           <t>31729.5</t>
         </is>
       </c>
-      <c r="AZ35" t="inlineStr">
-        <is>
-          <t>16801.32</t>
-        </is>
+      <c r="AZ35" t="n">
+        <v>16801.32</v>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
@@ -15530,8 +15324,10 @@
           <t>3201.791658960425</t>
         </is>
       </c>
-      <c r="BD35" t="n">
-        <v>7916</v>
+      <c r="BD35" t="inlineStr">
+        <is>
+          <t>7916.0</t>
+        </is>
       </c>
       <c r="BE35" t="inlineStr">
         <is>
@@ -15697,7 +15493,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -15881,15 +15677,11 @@
           <t>95.54</t>
         </is>
       </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>99.16</t>
-        </is>
-      </c>
-      <c r="AN36" t="inlineStr">
-        <is>
-          <t>102.56</t>
-        </is>
+      <c r="AM36" t="n">
+        <v>99.16</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>102.56</v>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
@@ -15936,20 +15728,16 @@
           <t>7550.0</t>
         </is>
       </c>
-      <c r="AX36" t="inlineStr">
-        <is>
-          <t>42357.4</t>
-        </is>
+      <c r="AX36" t="n">
+        <v>42357.4</v>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
           <t>32176.3</t>
         </is>
       </c>
-      <c r="AZ36" t="inlineStr">
-        <is>
-          <t>16923.88</t>
-        </is>
+      <c r="AZ36" t="n">
+        <v>16923.88</v>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
@@ -15966,8 +15754,10 @@
           <t>6140.811472509969</t>
         </is>
       </c>
-      <c r="BD36" t="n">
-        <v>7550</v>
+      <c r="BD36" t="inlineStr">
+        <is>
+          <t>7550.0</t>
+        </is>
       </c>
       <c r="BE36" t="inlineStr">
         <is>
@@ -16133,7 +15923,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -16317,15 +16107,11 @@
           <t>95.02000000000001</t>
         </is>
       </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>99.39</t>
-        </is>
-      </c>
-      <c r="AN37" t="inlineStr">
-        <is>
-          <t>102.63</t>
-        </is>
+      <c r="AM37" t="n">
+        <v>99.39</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>102.63</v>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
@@ -16372,20 +16158,16 @@
           <t>127346.0</t>
         </is>
       </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>45469.2</t>
-        </is>
+      <c r="AX37" t="n">
+        <v>45469.2</v>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
           <t>32539.5</t>
         </is>
       </c>
-      <c r="AZ37" t="inlineStr">
-        <is>
-          <t>16911.86</t>
-        </is>
+      <c r="AZ37" t="n">
+        <v>16911.86</v>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
@@ -16402,8 +16184,10 @@
           <t>10159.31079641968</t>
         </is>
       </c>
-      <c r="BD37" t="n">
-        <v>127346</v>
+      <c r="BD37" t="inlineStr">
+        <is>
+          <t>127346.0</t>
+        </is>
       </c>
       <c r="BE37" t="inlineStr">
         <is>
@@ -16569,7 +16353,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -16753,15 +16537,11 @@
           <t>95.1</t>
         </is>
       </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>99.77</t>
-        </is>
-      </c>
-      <c r="AN38" t="inlineStr">
-        <is>
-          <t>102.74</t>
-        </is>
+      <c r="AM38" t="n">
+        <v>99.77</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>102.74</v>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
@@ -16808,20 +16588,16 @@
           <t>31235.0</t>
         </is>
       </c>
-      <c r="AX38" t="inlineStr">
-        <is>
-          <t>26891.2</t>
-        </is>
+      <c r="AX38" t="n">
+        <v>26891.2</v>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
           <t>23743.9</t>
         </is>
       </c>
-      <c r="AZ38" t="inlineStr">
-        <is>
-          <t>14522.76</t>
-        </is>
+      <c r="AZ38" t="n">
+        <v>14522.76</v>
       </c>
       <c r="BA38" t="inlineStr">
         <is>
@@ -16838,8 +16614,10 @@
           <t>2701.905873561409</t>
         </is>
       </c>
-      <c r="BD38" t="n">
-        <v>31235</v>
+      <c r="BD38" t="inlineStr">
+        <is>
+          <t>31235.0</t>
+        </is>
       </c>
       <c r="BE38" t="inlineStr">
         <is>
@@ -17005,7 +16783,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -17189,15 +16967,11 @@
           <t>95.8</t>
         </is>
       </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>100.22</t>
-        </is>
-      </c>
-      <c r="AN39" t="inlineStr">
-        <is>
-          <t>102.88</t>
-        </is>
+      <c r="AM39" t="n">
+        <v>100.22</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>102.88</v>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
@@ -17244,20 +17018,16 @@
           <t>20123.0</t>
         </is>
       </c>
-      <c r="AX39" t="inlineStr">
-        <is>
-          <t>25107.0</t>
-        </is>
+      <c r="AX39" t="n">
+        <v>25107</v>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
           <t>21879.0</t>
         </is>
       </c>
-      <c r="AZ39" t="inlineStr">
-        <is>
-          <t>14111.6</t>
-        </is>
+      <c r="AZ39" t="n">
+        <v>14111.6</v>
       </c>
       <c r="BA39" t="inlineStr">
         <is>
@@ -17274,8 +17044,10 @@
           <t>2249.580773993839</t>
         </is>
       </c>
-      <c r="BD39" t="n">
-        <v>20123</v>
+      <c r="BD39" t="inlineStr">
+        <is>
+          <t>20123.0</t>
+        </is>
       </c>
       <c r="BE39" t="inlineStr">
         <is>
@@ -17441,7 +17213,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -17625,15 +17397,11 @@
           <t>96.75999999999999</t>
         </is>
       </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>100.72</t>
-        </is>
-      </c>
-      <c r="AN40" t="inlineStr">
-        <is>
-          <t>103.03</t>
-        </is>
+      <c r="AM40" t="n">
+        <v>100.72</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>103.03</v>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
@@ -17680,20 +17448,16 @@
           <t>25533.0</t>
         </is>
       </c>
-      <c r="AX40" t="inlineStr">
-        <is>
-          <t>24625.0</t>
-        </is>
+      <c r="AX40" t="n">
+        <v>24625</v>
       </c>
       <c r="AY40" t="inlineStr">
         <is>
           <t>21086.8</t>
         </is>
       </c>
-      <c r="AZ40" t="inlineStr">
-        <is>
-          <t>13809.16</t>
-        </is>
+      <c r="AZ40" t="n">
+        <v>13809.16</v>
       </c>
       <c r="BA40" t="inlineStr">
         <is>
@@ -17710,8 +17474,10 @@
           <t>2713.631318397525</t>
         </is>
       </c>
-      <c r="BD40" t="n">
-        <v>25533</v>
+      <c r="BD40" t="inlineStr">
+        <is>
+          <t>25533.0</t>
+        </is>
       </c>
       <c r="BE40" t="inlineStr">
         <is>
@@ -17877,7 +17643,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -18061,15 +17827,11 @@
           <t>98.25999999999999</t>
         </is>
       </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>101.22</t>
-        </is>
-      </c>
-      <c r="AN41" t="inlineStr">
-        <is>
-          <t>103.2</t>
-        </is>
+      <c r="AM41" t="n">
+        <v>101.22</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>103.2</v>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
@@ -18116,20 +17878,16 @@
           <t>23109.0</t>
         </is>
       </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>21995.2</t>
-        </is>
+      <c r="AX41" t="n">
+        <v>21995.2</v>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
           <t>19820.1</t>
         </is>
       </c>
-      <c r="AZ41" t="inlineStr">
-        <is>
-          <t>13506.86</t>
-        </is>
+      <c r="AZ41" t="n">
+        <v>13506.86</v>
       </c>
       <c r="BA41" t="inlineStr">
         <is>
@@ -18146,8 +17904,10 @@
           <t>2700.002406174313</t>
         </is>
       </c>
-      <c r="BD41" t="n">
-        <v>23109</v>
+      <c r="BD41" t="inlineStr">
+        <is>
+          <t>23109.0</t>
+        </is>
       </c>
       <c r="BE41" t="inlineStr">
         <is>
@@ -18313,7 +18073,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -18497,15 +18257,11 @@
           <t>99.04</t>
         </is>
       </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>101.64</t>
-        </is>
-      </c>
-      <c r="AN42" t="inlineStr">
-        <is>
-          <t>103.32</t>
-        </is>
+      <c r="AM42" t="n">
+        <v>101.64</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>103.32</v>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
@@ -18552,20 +18308,16 @@
           <t>34456.0</t>
         </is>
       </c>
-      <c r="AX42" t="inlineStr">
-        <is>
-          <t>19609.8</t>
-        </is>
+      <c r="AX42" t="n">
+        <v>19609.8</v>
       </c>
       <c r="AY42" t="inlineStr">
         <is>
           <t>18384.7</t>
         </is>
       </c>
-      <c r="AZ42" t="inlineStr">
-        <is>
-          <t>13213.0</t>
-        </is>
+      <c r="AZ42" t="n">
+        <v>13213</v>
       </c>
       <c r="BA42" t="inlineStr">
         <is>
@@ -18582,8 +18334,10 @@
           <t>2843.818159920644</t>
         </is>
       </c>
-      <c r="BD42" t="n">
-        <v>34456</v>
+      <c r="BD42" t="inlineStr">
+        <is>
+          <t>34456.0</t>
+        </is>
       </c>
       <c r="BE42" t="inlineStr">
         <is>
@@ -18749,7 +18503,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -18933,15 +18687,11 @@
           <t>99.28</t>
         </is>
       </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>102.0</t>
-        </is>
-      </c>
-      <c r="AN43" t="inlineStr">
-        <is>
-          <t>103.41</t>
-        </is>
+      <c r="AM43" t="n">
+        <v>102</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>103.41</v>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
@@ -18988,20 +18738,16 @@
           <t>22314.0</t>
         </is>
       </c>
-      <c r="AX43" t="inlineStr">
-        <is>
-          <t>20596.6</t>
-        </is>
+      <c r="AX43" t="n">
+        <v>20596.6</v>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
           <t>16009.5</t>
         </is>
       </c>
-      <c r="AZ43" t="inlineStr">
-        <is>
-          <t>12690.16</t>
-        </is>
+      <c r="AZ43" t="n">
+        <v>12690.16</v>
       </c>
       <c r="BA43" t="inlineStr">
         <is>
@@ -19018,8 +18764,10 @@
           <t>1731.954302418231</t>
         </is>
       </c>
-      <c r="BD43" t="n">
-        <v>22314</v>
+      <c r="BD43" t="inlineStr">
+        <is>
+          <t>22314.0</t>
+        </is>
       </c>
       <c r="BE43" t="inlineStr">
         <is>
@@ -19185,7 +18933,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -19369,15 +19117,11 @@
           <t>99.8</t>
         </is>
       </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>102.2</t>
-        </is>
-      </c>
-      <c r="AN44" t="inlineStr">
-        <is>
-          <t>103.46</t>
-        </is>
+      <c r="AM44" t="n">
+        <v>102.2</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>103.46</v>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
@@ -19424,20 +19168,16 @@
           <t>17713.0</t>
         </is>
       </c>
-      <c r="AX44" t="inlineStr">
-        <is>
-          <t>18651.0</t>
-        </is>
+      <c r="AX44" t="n">
+        <v>18651</v>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
           <t>14471.1</t>
         </is>
       </c>
-      <c r="AZ44" t="inlineStr">
-        <is>
-          <t>12507.46</t>
-        </is>
+      <c r="AZ44" t="n">
+        <v>12507.46</v>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
@@ -19454,8 +19194,10 @@
           <t>1382.650423756993</t>
         </is>
       </c>
-      <c r="BD44" t="n">
-        <v>17713</v>
+      <c r="BD44" t="inlineStr">
+        <is>
+          <t>17713.0</t>
+        </is>
       </c>
       <c r="BE44" t="inlineStr">
         <is>
@@ -19621,7 +19363,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -19805,15 +19547,11 @@
           <t>100.14</t>
         </is>
       </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>102.36</t>
-        </is>
-      </c>
-      <c r="AN45" t="inlineStr">
-        <is>
-          <t>103.51</t>
-        </is>
+      <c r="AM45" t="n">
+        <v>102.36</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>103.51</v>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
@@ -19860,20 +19598,16 @@
           <t>12384.0</t>
         </is>
       </c>
-      <c r="AX45" t="inlineStr">
-        <is>
-          <t>17548.6</t>
-        </is>
+      <c r="AX45" t="n">
+        <v>17548.6</v>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
           <t>13569.2</t>
         </is>
       </c>
-      <c r="AZ45" t="inlineStr">
-        <is>
-          <t>12507.7</t>
-        </is>
+      <c r="AZ45" t="n">
+        <v>12507.7</v>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
@@ -19890,8 +19624,10 @@
           <t>1327.228796249619</t>
         </is>
       </c>
-      <c r="BD45" t="n">
-        <v>12384</v>
+      <c r="BD45" t="inlineStr">
+        <is>
+          <t>12384.0</t>
+        </is>
       </c>
       <c r="BE45" t="inlineStr">
         <is>
@@ -20057,7 +19793,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -20241,15 +19977,11 @@
           <t>51.86</t>
         </is>
       </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>54.78</t>
-        </is>
-      </c>
-      <c r="AN46" t="inlineStr">
-        <is>
-          <t>58.02</t>
-        </is>
+      <c r="AM46" t="n">
+        <v>54.78</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>58.02</v>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
@@ -20296,20 +20028,16 @@
           <t>16370637.0</t>
         </is>
       </c>
-      <c r="AX46" t="inlineStr">
-        <is>
-          <t>14968564.6</t>
-        </is>
+      <c r="AX46" t="n">
+        <v>14968564.6</v>
       </c>
       <c r="AY46" t="inlineStr">
         <is>
           <t>25991927.5</t>
         </is>
       </c>
-      <c r="AZ46" t="inlineStr">
-        <is>
-          <t>55328963.9</t>
-        </is>
+      <c r="AZ46" t="n">
+        <v>55328963.9</v>
       </c>
       <c r="BA46" t="inlineStr">
         <is>
@@ -20326,8 +20054,10 @@
           <t>-3761738.343921479</t>
         </is>
       </c>
-      <c r="BD46" t="n">
-        <v>16370637</v>
+      <c r="BD46" t="inlineStr">
+        <is>
+          <t>16370637.0</t>
+        </is>
       </c>
       <c r="BE46" t="inlineStr">
         <is>
@@ -20493,7 +20223,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -20677,15 +20407,11 @@
           <t>51.73999999999999</t>
         </is>
       </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>55.01</t>
-        </is>
-      </c>
-      <c r="AN47" t="inlineStr">
-        <is>
-          <t>58.25</t>
-        </is>
+      <c r="AM47" t="n">
+        <v>55.01</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>58.25</v>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
@@ -20732,20 +20458,16 @@
           <t>14210191.0</t>
         </is>
       </c>
-      <c r="AX47" t="inlineStr">
-        <is>
-          <t>15743790.2</t>
-        </is>
+      <c r="AX47" t="n">
+        <v>15743790.2</v>
       </c>
       <c r="AY47" t="inlineStr">
         <is>
           <t>25956465.7</t>
         </is>
       </c>
-      <c r="AZ47" t="inlineStr">
-        <is>
-          <t>65312254.98</t>
-        </is>
+      <c r="AZ47" t="n">
+        <v>65312254.98</v>
       </c>
       <c r="BA47" t="inlineStr">
         <is>
@@ -20762,8 +20484,10 @@
           <t>-3880161.860334959</t>
         </is>
       </c>
-      <c r="BD47" t="n">
-        <v>14210191</v>
+      <c r="BD47" t="inlineStr">
+        <is>
+          <t>14210191.0</t>
+        </is>
       </c>
       <c r="BE47" t="inlineStr">
         <is>
@@ -20929,7 +20653,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -21113,15 +20837,11 @@
           <t>51.73999999999999</t>
         </is>
       </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>55.27</t>
-        </is>
-      </c>
-      <c r="AN48" t="inlineStr">
-        <is>
-          <t>58.46</t>
-        </is>
+      <c r="AM48" t="n">
+        <v>55.27</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>58.46</v>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
@@ -21168,20 +20888,16 @@
           <t>15825778.0</t>
         </is>
       </c>
-      <c r="AX48" t="inlineStr">
-        <is>
-          <t>21316600.4</t>
-        </is>
+      <c r="AX48" t="n">
+        <v>21316600.4</v>
       </c>
       <c r="AY48" t="inlineStr">
         <is>
           <t>25649746.9</t>
         </is>
       </c>
-      <c r="AZ48" t="inlineStr">
-        <is>
-          <t>67714501.66</t>
-        </is>
+      <c r="AZ48" t="n">
+        <v>67714501.66</v>
       </c>
       <c r="BA48" t="inlineStr">
         <is>
@@ -21198,8 +20914,10 @@
           <t>-3679284.745913677</t>
         </is>
       </c>
-      <c r="BD48" t="n">
-        <v>15825778</v>
+      <c r="BD48" t="inlineStr">
+        <is>
+          <t>15825778.0</t>
+        </is>
       </c>
       <c r="BE48" t="inlineStr">
         <is>
@@ -21365,7 +21083,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -21549,15 +21267,11 @@
           <t>52.14</t>
         </is>
       </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>55.59</t>
-        </is>
-      </c>
-      <c r="AN49" t="inlineStr">
-        <is>
-          <t>58.66</t>
-        </is>
+      <c r="AM49" t="n">
+        <v>55.59</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>58.66</v>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
@@ -21604,20 +21318,16 @@
           <t>17027345.0</t>
         </is>
       </c>
-      <c r="AX49" t="inlineStr">
-        <is>
-          <t>22754558.0</t>
-        </is>
+      <c r="AX49" t="n">
+        <v>22754558</v>
       </c>
       <c r="AY49" t="inlineStr">
         <is>
           <t>26782636.3</t>
         </is>
       </c>
-      <c r="AZ49" t="inlineStr">
-        <is>
-          <t>69191727.6</t>
-        </is>
+      <c r="AZ49" t="n">
+        <v>69191727.59999999</v>
       </c>
       <c r="BA49" t="inlineStr">
         <is>
@@ -21634,8 +21344,10 @@
           <t>-3434013.020100649</t>
         </is>
       </c>
-      <c r="BD49" t="n">
-        <v>17027345</v>
+      <c r="BD49" t="inlineStr">
+        <is>
+          <t>17027345.0</t>
+        </is>
       </c>
       <c r="BE49" t="inlineStr">
         <is>
@@ -21801,7 +21513,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -21985,15 +21697,11 @@
           <t>52.67999999999999</t>
         </is>
       </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>55.92</t>
-        </is>
-      </c>
-      <c r="AN50" t="inlineStr">
-        <is>
-          <t>58.83</t>
-        </is>
+      <c r="AM50" t="n">
+        <v>55.92</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>58.83</v>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
@@ -22040,20 +21748,16 @@
           <t>11408872.0</t>
         </is>
       </c>
-      <c r="AX50" t="inlineStr">
-        <is>
-          <t>28718377.4</t>
-        </is>
+      <c r="AX50" t="n">
+        <v>28718377.4</v>
       </c>
       <c r="AY50" t="inlineStr">
         <is>
           <t>27355481.5</t>
         </is>
       </c>
-      <c r="AZ50" t="inlineStr">
-        <is>
-          <t>69373581.34</t>
-        </is>
+      <c r="AZ50" t="n">
+        <v>69373581.34</v>
       </c>
       <c r="BA50" t="inlineStr">
         <is>
@@ -22070,8 +21774,10 @@
           <t>-3089720.839649871</t>
         </is>
       </c>
-      <c r="BD50" t="n">
-        <v>11408872</v>
+      <c r="BD50" t="inlineStr">
+        <is>
+          <t>11408872.0</t>
+        </is>
       </c>
       <c r="BE50" t="inlineStr">
         <is>
@@ -22237,7 +21943,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -22421,15 +22127,11 @@
           <t>53.23999999999999</t>
         </is>
       </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>56.26</t>
-        </is>
-      </c>
-      <c r="AN51" t="inlineStr">
-        <is>
-          <t>58.96</t>
-        </is>
+      <c r="AM51" t="n">
+        <v>56.26</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>58.96</v>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
@@ -22476,20 +22178,16 @@
           <t>20246765.0</t>
         </is>
       </c>
-      <c r="AX51" t="inlineStr">
-        <is>
-          <t>37015290.4</t>
-        </is>
+      <c r="AX51" t="n">
+        <v>37015290.4</v>
       </c>
       <c r="AY51" t="inlineStr">
         <is>
           <t>28888889.5</t>
         </is>
       </c>
-      <c r="AZ51" t="inlineStr">
-        <is>
-          <t>69945836.02</t>
-        </is>
+      <c r="AZ51" t="n">
+        <v>69945836.02</v>
       </c>
       <c r="BA51" t="inlineStr">
         <is>
@@ -22506,8 +22204,10 @@
           <t>-1885548.444732688</t>
         </is>
       </c>
-      <c r="BD51" t="n">
-        <v>20246765</v>
+      <c r="BD51" t="inlineStr">
+        <is>
+          <t>20246765.0</t>
+        </is>
       </c>
       <c r="BE51" t="inlineStr">
         <is>
@@ -22673,7 +22373,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -22857,15 +22557,11 @@
           <t>54.21999999999999</t>
         </is>
       </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>56.57</t>
-        </is>
-      </c>
-      <c r="AN52" t="inlineStr">
-        <is>
-          <t>59.12</t>
-        </is>
+      <c r="AM52" t="n">
+        <v>56.57</v>
+      </c>
+      <c r="AN52" t="n">
+        <v>59.12</v>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
@@ -22912,20 +22608,16 @@
           <t>42074242.0</t>
         </is>
       </c>
-      <c r="AX52" t="inlineStr">
-        <is>
-          <t>36169141.2</t>
-        </is>
+      <c r="AX52" t="n">
+        <v>36169141.2</v>
       </c>
       <c r="AY52" t="inlineStr">
         <is>
           <t>29060387.7</t>
         </is>
       </c>
-      <c r="AZ52" t="inlineStr">
-        <is>
-          <t>70323701.58</t>
-        </is>
+      <c r="AZ52" t="n">
+        <v>70323701.58</v>
       </c>
       <c r="BA52" t="inlineStr">
         <is>
@@ -22942,8 +22634,10 @@
           <t>-1044878.257539123</t>
         </is>
       </c>
-      <c r="BD52" t="n">
-        <v>42074242</v>
+      <c r="BD52" t="inlineStr">
+        <is>
+          <t>42074242.0</t>
+        </is>
       </c>
       <c r="BE52" t="inlineStr">
         <is>
@@ -23109,7 +22803,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -23293,15 +22987,11 @@
           <t>55.12</t>
         </is>
       </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>56.86</t>
-        </is>
-      </c>
-      <c r="AN53" t="inlineStr">
-        <is>
-          <t>59.28</t>
-        </is>
+      <c r="AM53" t="n">
+        <v>56.86</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>59.28</v>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
@@ -23348,20 +23038,16 @@
           <t>23015566.0</t>
         </is>
       </c>
-      <c r="AX53" t="inlineStr">
-        <is>
-          <t>29982893.4</t>
-        </is>
+      <c r="AX53" t="n">
+        <v>29982893.4</v>
       </c>
       <c r="AY53" t="inlineStr">
         <is>
           <t>27325142.8</t>
         </is>
       </c>
-      <c r="AZ53" t="inlineStr">
-        <is>
-          <t>70871687.6</t>
-        </is>
+      <c r="AZ53" t="n">
+        <v>70871687.59999999</v>
       </c>
       <c r="BA53" t="inlineStr">
         <is>
@@ -23378,8 +23064,10 @@
           <t>-2145262.016636197</t>
         </is>
       </c>
-      <c r="BD53" t="n">
-        <v>23015566</v>
+      <c r="BD53" t="inlineStr">
+        <is>
+          <t>23015566.0</t>
+        </is>
       </c>
       <c r="BE53" t="inlineStr">
         <is>
@@ -23545,7 +23233,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -23729,15 +23417,11 @@
           <t>55.72000000000001</t>
         </is>
       </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>57.07</t>
-        </is>
-      </c>
-      <c r="AN54" t="inlineStr">
-        <is>
-          <t>59.42</t>
-        </is>
+      <c r="AM54" t="n">
+        <v>57.07</v>
+      </c>
+      <c r="AN54" t="n">
+        <v>59.42</v>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
@@ -23784,20 +23468,16 @@
           <t>46846442.0</t>
         </is>
       </c>
-      <c r="AX54" t="inlineStr">
-        <is>
-          <t>30810714.6</t>
-        </is>
+      <c r="AX54" t="n">
+        <v>30810714.6</v>
       </c>
       <c r="AY54" t="inlineStr">
         <is>
           <t>28427276.6</t>
         </is>
       </c>
-      <c r="AZ54" t="inlineStr">
-        <is>
-          <t>71965384.46</t>
-        </is>
+      <c r="AZ54" t="n">
+        <v>71965384.45999999</v>
       </c>
       <c r="BA54" t="inlineStr">
         <is>
@@ -23814,8 +23494,10 @@
           <t>-1598621.314752154</t>
         </is>
       </c>
-      <c r="BD54" t="n">
-        <v>46846442</v>
+      <c r="BD54" t="inlineStr">
+        <is>
+          <t>46846442.0</t>
+        </is>
       </c>
       <c r="BE54" t="inlineStr">
         <is>
@@ -23981,7 +23663,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -24165,15 +23847,11 @@
           <t>56.22000000000001</t>
         </is>
       </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>57.31</t>
-        </is>
-      </c>
-      <c r="AN55" t="inlineStr">
-        <is>
-          <t>59.56</t>
-        </is>
+      <c r="AM55" t="n">
+        <v>57.31</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>59.56</v>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
@@ -24220,20 +23898,16 @@
           <t>52893437.0</t>
         </is>
       </c>
-      <c r="AX55" t="inlineStr">
-        <is>
-          <t>25992585.6</t>
-        </is>
+      <c r="AX55" t="n">
+        <v>25992585.6</v>
       </c>
       <c r="AY55" t="inlineStr">
         <is>
           <t>25254632.5</t>
         </is>
       </c>
-      <c r="AZ55" t="inlineStr">
-        <is>
-          <t>72823093.42</t>
-        </is>
+      <c r="AZ55" t="n">
+        <v>72823093.42</v>
       </c>
       <c r="BA55" t="inlineStr">
         <is>
@@ -24250,8 +23924,10 @@
           <t>-3313920.550819516</t>
         </is>
       </c>
-      <c r="BD55" t="n">
-        <v>52893437</v>
+      <c r="BD55" t="inlineStr">
+        <is>
+          <t>52893437.0</t>
+        </is>
       </c>
       <c r="BE55" t="inlineStr">
         <is>
@@ -24417,7 +24093,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -24601,15 +24277,11 @@
           <t>56.66</t>
         </is>
       </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>57.52</t>
-        </is>
-      </c>
-      <c r="AN56" t="inlineStr">
-        <is>
-          <t>59.68</t>
-        </is>
+      <c r="AM56" t="n">
+        <v>57.52</v>
+      </c>
+      <c r="AN56" t="n">
+        <v>59.68</v>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
@@ -24656,20 +24328,16 @@
           <t>16016019.0</t>
         </is>
       </c>
-      <c r="AX56" t="inlineStr">
-        <is>
-          <t>20762488.6</t>
-        </is>
+      <c r="AX56" t="n">
+        <v>20762488.6</v>
       </c>
       <c r="AY56" t="inlineStr">
         <is>
           <t>23044675.4</t>
         </is>
       </c>
-      <c r="AZ56" t="inlineStr">
-        <is>
-          <t>73396602.94</t>
-        </is>
+      <c r="AZ56" t="n">
+        <v>73396602.94</v>
       </c>
       <c r="BA56" t="inlineStr">
         <is>
@@ -24686,8 +24354,10 @@
           <t>-6293886.04695791</t>
         </is>
       </c>
-      <c r="BD56" t="n">
-        <v>16016019</v>
+      <c r="BD56" t="inlineStr">
+        <is>
+          <t>16016019.0</t>
+        </is>
       </c>
       <c r="BE56" t="inlineStr">
         <is>
